--- a/data/trans_dic/IP11-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses.</t>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,51</t>
+          <t>3,73; 16,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,25</t>
+          <t>1,03; 9,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 10,34</t>
+          <t>1,05; 10,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 21,92</t>
+          <t>6,58; 21,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,68</t>
+          <t>3,69; 16,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 18,12</t>
+          <t>4,45; 17,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,62</t>
+          <t>1,53; 13,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 16,58</t>
+          <t>6,78; 16,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,39</t>
+          <t>2,06; 8,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 11,64</t>
+          <t>3,69; 11,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,91</t>
+          <t>1,97; 9,45</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,9</t>
+          <t>0,62; 5,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,4</t>
+          <t>5,23; 14,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,63</t>
+          <t>2,54; 10,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,32</t>
+          <t>0,53; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,36; 15,32</t>
+          <t>5,7; 14,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 10,34</t>
+          <t>3,06; 11,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,12</t>
+          <t>1,55; 8,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,63</t>
+          <t>0,62; 3,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,12</t>
+          <t>6,37; 12,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,62</t>
+          <t>3,48; 8,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,63</t>
+          <t>1,52; 6,01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 15,48</t>
+          <t>3,86; 14,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,58; 25,65</t>
+          <t>10,32; 24,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,52</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 10,22</t>
+          <t>0,7; 10,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 14,28</t>
+          <t>4,51; 14,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,53; 27,48</t>
+          <t>12,18; 28,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,5</t>
+          <t>0,81; 8,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 13,11</t>
+          <t>5,28; 13,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,94; 23,62</t>
+          <t>13,42; 23,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,13</t>
+          <t>0,48; 4,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,67</t>
+          <t>1,21; 6,18</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 15,22</t>
+          <t>4,74; 14,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,52</t>
+          <t>0,84; 8,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 12,48</t>
+          <t>2,59; 13,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 17,0</t>
+          <t>5,54; 16,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,55</t>
+          <t>2,03; 11,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 16,35</t>
+          <t>5,13; 16,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 10,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,31</t>
+          <t>6,1; 14,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,63</t>
+          <t>2,05; 8,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,33</t>
+          <t>4,95; 12,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,62</t>
+          <t>0,35; 5,48</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 15,02</t>
+          <t>1,7; 14,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,88</t>
+          <t>1,54; 12,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 11,43</t>
+          <t>1,38; 11,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,5</t>
+          <t>0,82; 7,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,64</t>
+          <t>1,52; 8,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,56</t>
+          <t>0,66; 6,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,84; 23,59</t>
+          <t>7,47; 23,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 14,3</t>
+          <t>1,4; 13,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,75; 15,58</t>
+          <t>3,14; 15,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,02</t>
+          <t>2,07; 10,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,49; 31,83</t>
+          <t>13,93; 32,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,88; 18,47</t>
+          <t>5,13; 19,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,44</t>
+          <t>1,11; 10,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,84</t>
+          <t>1,68; 7,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 24,52</t>
+          <t>12,82; 24,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,6</t>
+          <t>4,56; 13,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 10,91</t>
+          <t>2,54; 9,57</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,11</t>
+          <t>2,67; 9,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,17</t>
+          <t>5,04; 13,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,2</t>
+          <t>0,57; 4,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,42</t>
+          <t>1,32; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,11; 12,94</t>
+          <t>5,43; 12,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 19,72</t>
+          <t>10,02; 19,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,58</t>
+          <t>1,2; 5,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,87</t>
+          <t>2,16; 8,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,68; 9,68</t>
+          <t>4,58; 9,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,78; 15,05</t>
+          <t>8,53; 14,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,23</t>
+          <t>1,22; 4,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,02</t>
+          <t>2,32; 6,11</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,43</t>
+          <t>1,3; 6,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,12</t>
+          <t>1,8; 6,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,94</t>
+          <t>0,7; 3,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,22</t>
+          <t>2,91; 8,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,91</t>
+          <t>0,84; 5,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,28</t>
+          <t>1,92; 6,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,18</t>
+          <t>2,49; 6,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,73</t>
+          <t>1,49; 4,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,66</t>
+          <t>1,79; 4,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,65</t>
+          <t>3,99; 6,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,93</t>
+          <t>5,82; 8,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,48</t>
+          <t>2,42; 4,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,81</t>
+          <t>1,61; 3,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,09</t>
+          <t>5,1; 8,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,67</t>
+          <t>8,08; 11,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,04</t>
+          <t>4,21; 7,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,62</t>
+          <t>2,17; 4,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,9</t>
+          <t>4,91; 6,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,83</t>
+          <t>7,37; 9,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,45</t>
+          <t>3,62; 5,35</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,83</t>
+          <t>2,14; 3,74</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han sufrido algún accidente por el cual necesitase asiscencia sanitaria en los últimos 12 meses. (tasa de respuesta: 99,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6165</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3804</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12133</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5658</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8545</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1960; 8683</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>591; 5361</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>771; 7887</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3963; 12859</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2388; 10742</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2866; 11107</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1211; 10358</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7650; 18562</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2513; 10484</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4491; 14469</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3004; 14419</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5353</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6802</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5109</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19860</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>12155</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>8020</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>630; 5871</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5479; 15359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2613; 10390</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>680; 7284</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4438</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6303; 16137</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3352; 12653</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1961; 10699</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1312; 7457</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>13702; 27717</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7410; 18438</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3852; 15262</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5583</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11322</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>11805</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25050</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2226</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2611; 10080</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7035; 16625</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3942</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>408; 5971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3169; 10114</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8675; 20102</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5227</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>546; 5501</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>7282; 18347</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>18709; 33365</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>654; 6097</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1523; 7757</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>6832</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7997</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7834</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>14829</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>7318</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12780</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>3545; 11074</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>648; 6502</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1997; 10207</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4379; 13381</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1671; 9603</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4165; 13255</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8203</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9398; 21689</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3272; 13957</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>7833; 19510</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>512; 8119</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2790</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2089</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2790</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>4063</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>710; 6107</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>677; 5573</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3060</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>644; 5361</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4491</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3225</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>712; 6244</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1375; 7909</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>591; 5690</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3293</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7878</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3462</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>13152</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2320</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>21030</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4200</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4184; 13074</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>758; 7180</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1449; 7205</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1236; 6555</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8242; 19134</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2964; 11132</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>623; 6158</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1947; 8998</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>14761; 28688</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5104; 15072</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2598; 9793</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6846</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11955</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4003</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>11682</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>20472</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6837</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18528</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32428</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6578</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>10840</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3436; 12699</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6990; 18245</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>781; 6680</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1647; 8591</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7366; 17265</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>14608; 28899</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1732; 7809</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>3374; 12883</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>12105; 26078</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24251; 42339</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3424; 12135</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6510; 17141</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4875</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>810</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>7244</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>13410</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>9680</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>10362</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>2051; 9511</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2957; 10608</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1142; 6362</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3915</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>4769; 13636</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1441; 8638</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3273; 11824</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4812</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>8023; 19500</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4991; 15126</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5956; 16114</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5924</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>35304</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>51712</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>23369</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>17151</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>81829</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>125089</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>64093</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>41185</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>27177; 45823</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>41383; 63152</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>16956; 32398</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10722; 24148</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>36857; 57878</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>60681; 88164</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>31315; 52415</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>16495; 34648</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>68914; 97386</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>107822; 143696</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>52335; 77356</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>30595; 53334</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 16,52</t>
+          <t>3,81; 16,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,34</t>
+          <t>1,08; 9,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,76</t>
+          <t>1,03; 10,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 21,35</t>
+          <t>6,34; 20,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,57</t>
+          <t>3,41; 15,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 17,23</t>
+          <t>4,5; 18,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,05</t>
+          <t>1,45; 14,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 16,46</t>
+          <t>6,35; 16,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,58</t>
+          <t>2,02; 8,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 11,88</t>
+          <t>3,75; 12,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 9,45</t>
+          <t>1,74; 8,99</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,78</t>
+          <t>0,62; 6,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 14,67</t>
+          <t>5,23; 14,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,08</t>
+          <t>2,13; 9,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,72</t>
+          <t>0,59; 5,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,6</t>
+          <t>5,54; 14,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 11,54</t>
+          <t>3,14; 11,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,46</t>
+          <t>1,53; 8,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,55</t>
+          <t>0,84; 3,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 12,88</t>
+          <t>6,41; 12,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 8,67</t>
+          <t>3,51; 8,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,01</t>
+          <t>1,47; 5,92</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 14,91</t>
+          <t>3,91; 15,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 24,38</t>
+          <t>9,46; 24,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 10,25</t>
+          <t>0,71; 10,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 14,38</t>
+          <t>4,48; 15,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 28,21</t>
+          <t>11,71; 27,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,19</t>
+          <t>0,8; 8,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 13,3</t>
+          <t>5,2; 13,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,42; 23,93</t>
+          <t>13,13; 23,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,46</t>
+          <t>0,48; 4,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,18</t>
+          <t>1,14; 6,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,74; 14,79</t>
+          <t>4,71; 14,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,41</t>
+          <t>0,86; 8,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 13,26</t>
+          <t>2,83; 12,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 16,91</t>
+          <t>5,15; 16,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 11,68</t>
+          <t>2,0; 11,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 16,33</t>
+          <t>4,47; 15,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,5</t>
+          <t>0,0; 9,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 14,09</t>
+          <t>6,09; 14,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,75</t>
+          <t>2,17; 8,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,34</t>
+          <t>5,07; 12,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,48</t>
+          <t>0,35; 6,15</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,59</t>
+          <t>1,72; 15,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,69</t>
+          <t>1,55; 12,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1302,37 +1302,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,47</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,2</t>
+          <t>0,82; 7,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,72</t>
+          <t>1,55; 8,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,38</t>
+          <t>0,67; 6,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 23,35</t>
+          <t>7,74; 22,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,4; 13,23</t>
+          <t>2,41; 14,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 15,61</t>
+          <t>3,27; 16,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 10,97</t>
+          <t>1,94; 10,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 32,34</t>
+          <t>14,46; 32,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 19,28</t>
+          <t>4,99; 18,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,96</t>
+          <t>1,11; 10,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,77</t>
+          <t>1,67; 7,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,82; 24,91</t>
+          <t>12,74; 25,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,46</t>
+          <t>4,57; 13,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,57</t>
+          <t>2,77; 10,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,87</t>
+          <t>2,67; 9,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 13,15</t>
+          <t>5,56; 12,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,86</t>
+          <t>0,45; 4,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,9</t>
+          <t>1,33; 6,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,73</t>
+          <t>5,15; 13,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 19,83</t>
+          <t>9,72; 18,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,42</t>
+          <t>0,93; 5,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,26</t>
+          <t>2,14; 8,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,87</t>
+          <t>4,67; 9,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,88</t>
+          <t>8,94; 14,82</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,31</t>
+          <t>1,2; 4,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,11</t>
+          <t>2,27; 6,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,02</t>
+          <t>1,29; 6,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,44</t>
+          <t>1,48; 6,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,91</t>
+          <t>0,88; 3,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,31</t>
+          <t>2,79; 8,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,06</t>
+          <t>0,85; 4,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,92</t>
+          <t>2,29; 7,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,06</t>
+          <t>2,79; 6,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,51</t>
+          <t>1,65; 4,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,83</t>
+          <t>1,92; 4,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,73</t>
+          <t>3,85; 6,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,88</t>
+          <t>5,71; 9,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,61</t>
+          <t>2,45; 4,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,63</t>
+          <t>1,6; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 8,01</t>
+          <t>5,07; 8,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,08; 11,74</t>
+          <t>8,06; 11,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,05</t>
+          <t>4,22; 7,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,55</t>
+          <t>2,15; 4,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,94</t>
+          <t>4,92; 6,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,83</t>
+          <t>7,43; 9,73</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,35</t>
+          <t>3,65; 5,32</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,74</t>
+          <t>2,1; 3,69</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1960; 8683</t>
+          <t>2001; 8590</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2393</t>
+          <t>0; 2674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591; 5361</t>
+          <t>619; 5651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>771; 7887</t>
+          <t>753; 7389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3963; 12859</t>
+          <t>3819; 12258</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2388; 10742</t>
+          <t>2210; 10164</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2866; 11107</t>
+          <t>2898; 11628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1211; 10358</t>
+          <t>1150; 11211</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7650; 18562</t>
+          <t>7158; 18338</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2513; 10484</t>
+          <t>2475; 10580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4491; 14469</t>
+          <t>4565; 15233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3004; 14419</t>
+          <t>2657; 13725</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>630; 5871</t>
+          <t>631; 6427</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5479; 15359</t>
+          <t>5472; 15388</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2613; 10390</t>
+          <t>2193; 10189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>680; 7284</t>
+          <t>741; 7307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4394</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6303; 16137</t>
+          <t>6126; 16384</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3352; 12653</t>
+          <t>3445; 12219</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1961; 10699</t>
+          <t>1934; 10739</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1312; 7457</t>
+          <t>1766; 8056</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13702; 27717</t>
+          <t>13797; 27530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7410; 18438</t>
+          <t>7460; 18766</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3852; 15262</t>
+          <t>3711; 14976</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2611; 10080</t>
+          <t>2643; 10148</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7035; 16625</t>
+          <t>6449; 16790</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408; 5971</t>
+          <t>412; 6008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3169; 10114</t>
+          <t>3153; 11209</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8675; 20102</t>
+          <t>8347; 19401</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>546; 5501</t>
+          <t>537; 5562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7282; 18347</t>
+          <t>7166; 18720</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18709; 33365</t>
+          <t>18312; 33374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>654; 6097</t>
+          <t>657; 5991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1523; 7757</t>
+          <t>1429; 8495</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3545; 11074</t>
+          <t>3527; 11116</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>648; 6502</t>
+          <t>665; 6268</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1997; 10207</t>
+          <t>2178; 9644</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 4707</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4379; 13381</t>
+          <t>4077; 12942</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1671; 9603</t>
+          <t>1648; 9574</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4165; 13255</t>
+          <t>3633; 12851</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 8203</t>
+          <t>0; 7783</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9398; 21689</t>
+          <t>9373; 21729</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3272; 13957</t>
+          <t>3461; 13139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7833; 19510</t>
+          <t>8025; 19243</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>512; 8119</t>
+          <t>526; 9123</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>710; 6107</t>
+          <t>721; 6371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>677; 5573</t>
+          <t>679; 5495</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3060</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>644; 5361</t>
+          <t>0; 5369</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4491</t>
+          <t>0; 4402</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>712; 6244</t>
+          <t>709; 6862</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1375; 7909</t>
+          <t>1402; 7584</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>591; 5690</t>
+          <t>598; 5731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3293</t>
+          <t>0; 3735</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4565</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4184; 13074</t>
+          <t>4336; 12503</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>758; 7180</t>
+          <t>1306; 7778</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1449; 7205</t>
+          <t>1508; 7572</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1236; 6555</t>
+          <t>1157; 6550</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8242; 19134</t>
+          <t>8557; 19372</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2964; 11132</t>
+          <t>2884; 10479</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>623; 6158</t>
+          <t>623; 5955</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1947; 8998</t>
+          <t>1939; 8628</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14761; 28688</t>
+          <t>14668; 29051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5104; 15072</t>
+          <t>5114; 15116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2598; 9793</t>
+          <t>2840; 11206</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3436; 12699</t>
+          <t>3428; 11670</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6990; 18245</t>
+          <t>7713; 18020</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>781; 6680</t>
+          <t>623; 6517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1647; 8591</t>
+          <t>1654; 8434</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>7366; 17265</t>
+          <t>6991; 18185</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14608; 28899</t>
+          <t>14165; 27418</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1732; 7809</t>
+          <t>1335; 7982</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3374; 12883</t>
+          <t>3336; 12863</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12105; 26078</t>
+          <t>12346; 25982</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24251; 42339</t>
+          <t>25437; 42162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3424; 12135</t>
+          <t>3364; 11274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6510; 17141</t>
+          <t>6363; 17204</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2051; 9511</t>
+          <t>2044; 9567</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2957; 10608</t>
+          <t>2431; 9990</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1142; 6362</t>
+          <t>1427; 6353</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3915</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4769; 13636</t>
+          <t>4577; 13447</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1441; 8638</t>
+          <t>1456; 8277</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3273; 11824</t>
+          <t>3919; 12479</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8023; 19500</t>
+          <t>8980; 20164</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4991; 15126</t>
+          <t>5533; 15270</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5956; 16114</t>
+          <t>6402; 16255</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5924</t>
+          <t>0; 6031</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>27177; 45823</t>
+          <t>26187; 45694</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>41383; 63152</t>
+          <t>40579; 65077</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16956; 32398</t>
+          <t>17224; 31776</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10722; 24148</t>
+          <t>10652; 25105</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36857; 57878</t>
+          <t>36605; 58829</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60681; 88164</t>
+          <t>60540; 87567</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31315; 52415</t>
+          <t>31377; 52052</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>16495; 34648</t>
+          <t>16368; 35058</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>68914; 97386</t>
+          <t>69001; 96090</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107822; 143696</t>
+          <t>108681; 142229</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52335; 77356</t>
+          <t>52697; 76910</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>30595; 53334</t>
+          <t>29937; 52614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,75%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 16,34</t>
+          <t>6,6; 21,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>3,69; 16,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,85</t>
+          <t>4,61; 18,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,08</t>
+          <t>1,2; 12,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 20,36</t>
+          <t>3,62; 16,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 15,68</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 18,04</t>
+          <t>1,1; 10,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 14,13</t>
+          <t>1,22; 12,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 16,26</t>
+          <t>6,39; 16,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,66</t>
+          <t>2,08; 9,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 12,5</t>
+          <t>3,56; 11,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,99</t>
+          <t>2,26; 10,38</t>
         </is>
       </c>
     </row>
@@ -789,54 +789,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,19%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>9,23%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>5,72%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,33</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 14,7</t>
+          <t>5,36; 15,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,89</t>
+          <t>3,21; 10,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,78</t>
+          <t>1,47; 8,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,62; 5,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 14,82</t>
+          <t>5,2; 14,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 11,15</t>
+          <t>2,52; 9,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,49</t>
+          <t>0,78; 8,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,83</t>
+          <t>0,62; 3,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,79</t>
+          <t>6,37; 13,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,82</t>
+          <t>3,57; 8,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,92</t>
+          <t>1,73; 6,86</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8,85%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,61%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 15,01</t>
+          <t>4,38; 14,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 24,63</t>
+          <t>12,53; 27,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 10,31</t>
+          <t>0,75; 7,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,94</t>
+          <t>4,06; 15,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 27,23</t>
+          <t>10,58; 25,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,28</t>
+          <t>0,55; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 13,57</t>
+          <t>5,19; 13,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,13; 23,94</t>
+          <t>12,94; 23,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,38</t>
+          <t>0,47; 4,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,77</t>
+          <t>1,34; 6,75</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,13%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,65%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 14,85</t>
+          <t>5,67; 17,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,1</t>
+          <t>2,03; 11,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 12,53</t>
+          <t>4,63; 16,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 16,36</t>
+          <t>4,77; 15,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,64</t>
+          <t>0,84; 8,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 15,83</t>
+          <t>2,58; 12,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,96</t>
+          <t>0,0; 7,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 14,11</t>
+          <t>6,4; 14,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,23</t>
+          <t>2,08; 8,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,17</t>
+          <t>4,88; 12,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 6,15</t>
+          <t>0,34; 6,89</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,67%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>3,22%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,52</t>
+          <t>1,37; 11,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,69; 15,02</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,53; 12,88</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,86</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,48</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,63</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,92</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,92</t>
+          <t>0,83; 7,5</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,37</t>
+          <t>2,12; 9,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,43</t>
+          <t>0,66; 5,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,97</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,23%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,43%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>14,07%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>2,09; 11,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,33</t>
+          <t>14,49; 31,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 14,33</t>
+          <t>4,88; 18,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,4</t>
+          <t>1,03; 11,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 10,97</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,46; 32,75</t>
+          <t>7,84; 23,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 18,15</t>
+          <t>2,53; 14,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,6</t>
+          <t>2,55; 15,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,45</t>
+          <t>1,68; 7,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,74; 25,23</t>
+          <t>12,94; 24,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 13,5</t>
+          <t>4,48; 13,6</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,95</t>
+          <t>2,62; 11,0</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8,61%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,32%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 9,07</t>
+          <t>5,11; 12,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,99</t>
+          <t>9,96; 19,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,74</t>
+          <t>0,95; 5,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,77</t>
+          <t>2,31; 8,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,41</t>
+          <t>2,67; 9,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 18,81</t>
+          <t>5,4; 13,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,54</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 8,24</t>
+          <t>1,27; 6,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,67; 9,83</t>
+          <t>4,68; 9,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 14,82</t>
+          <t>8,78; 15,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,01</t>
+          <t>1,16; 4,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,13</t>
+          <t>2,34; 6,51</t>
         </is>
       </c>
     </row>
@@ -1629,62 +1629,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,92%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,06</t>
+          <t>2,76; 8,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,07</t>
+          <t>1,17; 4,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,9</t>
+          <t>2,25; 7,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,2</t>
+          <t>1,48; 6,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,85</t>
+          <t>1,68; 6,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,3</t>
+          <t>0,85; 3,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,26</t>
+          <t>2,63; 6,18</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,55</t>
+          <t>1,7; 4,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,87</t>
+          <t>1,83; 4,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,71</t>
+          <t>5,08; 8,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,15</t>
+          <t>8,14; 11,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,53</t>
+          <t>4,12; 7,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,78</t>
+          <t>2,14; 4,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,14</t>
+          <t>3,85; 6,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,66</t>
+          <t>5,81; 8,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,0</t>
+          <t>2,3; 4,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,61</t>
+          <t>1,89; 4,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,85</t>
+          <t>4,98; 6,9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,73</t>
+          <t>7,41; 9,83</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,32</t>
+          <t>3,64; 5,45</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,69</t>
+          <t>2,24; 3,81</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7535</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6165</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>4598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3145</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7535</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5178</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6165</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>5980</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2001; 8590</t>
+          <t>3972; 13198</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2674</t>
+          <t>2391; 10809</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>619; 5651</t>
+          <t>2972; 11682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>753; 7389</t>
+          <t>767; 8092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3819; 12258</t>
+          <t>1902; 8679</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2210; 10164</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2898; 11628</t>
+          <t>631; 5878</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1150; 11211</t>
+          <t>688; 7303</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7158; 18338</t>
+          <t>7208; 18704</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2475; 10580</t>
+          <t>2539; 11474</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4565; 15233</t>
+          <t>4338; 14181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2657; 13725</t>
+          <t>2725; 12516</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1341</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10203</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6802</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4753</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2419</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9658</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5353</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>10203</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6802</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7912</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>631; 6427</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5472; 15388</t>
+          <t>5930; 16936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2193; 10189</t>
+          <t>3521; 11336</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>741; 7307</t>
+          <t>1693; 9568</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>625; 5997</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6126; 16384</t>
+          <t>5446; 15082</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3445; 12219</t>
+          <t>2602; 9927</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1934; 10739</t>
+          <t>786; 8028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1766; 8056</t>
+          <t>1302; 7634</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13797; 27530</t>
+          <t>13702; 28250</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7460; 18766</t>
+          <t>7594; 18336</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3711; 14976</t>
+          <t>3712; 14761</t>
         </is>
       </c>
     </row>
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13729</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1666</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5583</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11322</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>759</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6222</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13729</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3426</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2643; 10148</t>
+          <t>3078; 10041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6449; 16790</t>
+          <t>8925; 19580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>0; 5027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>412; 6008</t>
+          <t>447; 4338</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3153; 11209</t>
+          <t>2743; 10464</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8347; 19401</t>
+          <t>7211; 17490</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4413</t>
+          <t>0; 5028</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>537; 5562</t>
+          <t>311; 5682</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7166; 18720</t>
+          <t>7154; 18075</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18312; 33374</t>
+          <t>18048; 32929</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>657; 5991</t>
+          <t>649; 5647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1429; 8495</t>
+          <t>1556; 7827</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7997</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4593</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7834</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6832</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2726</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4946</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7997</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7834</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3030</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3527; 11116</t>
+          <t>4484; 13450</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>665; 6268</t>
+          <t>1672; 9497</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2178; 9644</t>
+          <t>3762; 13272</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4707</t>
+          <t>0; 9410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4077; 12942</t>
+          <t>3572; 11397</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1648; 9574</t>
+          <t>653; 6593</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3633; 12851</t>
+          <t>1989; 9605</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7783</t>
+          <t>0; 5074</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9373; 21729</t>
+          <t>9857; 22027</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3461; 13139</t>
+          <t>3325; 13765</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8025; 19243</t>
+          <t>7716; 19495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>526; 9123</t>
+          <t>479; 9855</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,44 +2973,44 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2790</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2089</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1324</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
           <t>2790</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1083</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>721; 6371</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>679; 5495</t>
+          <t>641; 5343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3213</t>
+          <t>0; 4390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 3663</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>707; 6286</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>672; 5653</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3414</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 5369</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4402</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4040</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>709; 6862</t>
+          <t>717; 6505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1402; 7584</t>
+          <t>1926; 8736</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>598; 5731</t>
+          <t>593; 4956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3735</t>
+          <t>0; 3714</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13152</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>7878</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3545</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13152</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5974</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4565</t>
+          <t>1249; 6584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4336; 12503</t>
+          <t>8571; 18831</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1306; 7778</t>
+          <t>2816; 10666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1508; 7572</t>
+          <t>504; 5491</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1157; 6550</t>
+          <t>0; 4285</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8557; 19372</t>
+          <t>4387; 13206</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2884; 10479</t>
+          <t>1371; 7762</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>623; 5955</t>
+          <t>1169; 7121</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1939; 8628</t>
+          <t>1945; 9078</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14668; 29051</t>
+          <t>14903; 28238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5114; 15116</t>
+          <t>5016; 15234</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2840; 11206</t>
+          <t>2477; 10416</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>11682</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>20472</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>6854</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>6846</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>11955</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2663</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>11682</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>20472</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3915</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>10775</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3428; 11670</t>
+          <t>6932; 17557</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7713; 18020</t>
+          <t>14519; 28739</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623; 6517</t>
+          <t>1373; 8034</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1654; 8434</t>
+          <t>3263; 12058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6991; 18185</t>
+          <t>3432; 11711</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14165; 27418</t>
+          <t>7488; 18264</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1335; 7982</t>
+          <t>764; 7142</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3336; 12863</t>
+          <t>1559; 7989</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12346; 25982</t>
+          <t>12381; 25584</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25437; 42162</t>
+          <t>24968; 42807</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3364; 11274</t>
+          <t>3278; 11892</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6363; 17204</t>
+          <t>6187; 17185</t>
         </is>
       </c>
     </row>
@@ -3529,37 +3529,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4075</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7244</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>4875</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>5605</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>3118</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8536</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>4075</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7244</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>919</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1873</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2044; 9567</t>
+          <t>4521; 13492</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2431; 9990</t>
+          <t>1999; 8370</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1427; 6353</t>
+          <t>3844; 12443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4253</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4577; 13447</t>
+          <t>2335; 10149</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1456; 8277</t>
+          <t>2764; 10075</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3919; 12479</t>
+          <t>1377; 6405</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>0; 5112</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8980; 20164</t>
+          <t>8459; 19887</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5533; 15270</t>
+          <t>5696; 15862</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6402; 16255</t>
+          <t>6116; 15549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 6031</t>
+          <t>0; 5906</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>26187; 45694</t>
+          <t>36682; 58494</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>40579; 65077</t>
+          <t>61136; 87643</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17224; 31776</t>
+          <t>30622; 52365</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10652; 25105</t>
+          <t>14992; 32709</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36605; 58829</t>
+          <t>26221; 45310</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60540; 87567</t>
+          <t>41292; 63464</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31377; 52052</t>
+          <t>16176; 31456</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>16368; 35058</t>
+          <t>11864; 25644</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>69001; 96090</t>
+          <t>69862; 96898</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108681; 142229</t>
+          <t>108382; 143766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52697; 76910</t>
+          <t>52656; 78791</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29937; 52614</t>
+          <t>29723; 50648</t>
         </is>
       </c>
     </row>
